--- a/School_Mang/EXCEL/Final/Term_A/Term_A_3_Test.xlsx
+++ b/School_Mang/EXCEL/Final/Term_A/Term_A_3_Test.xlsx
@@ -167,14 +167,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -545,7 +538,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J152"/>
+  <dimension ref="A2:AD152"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="0" style="1" hidden="1" customWidth="1"/>
@@ -554,7 +547,7 @@
     <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -565,7 +558,7 @@
       <c r="I2" s="11"/>
       <c r="J2" s="11"/>
     </row>
-    <row r="3" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="8"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -576,7 +569,7 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -608,7 +601,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B5" s="10"/>
       <c r="C5" s="6">
         <v>0</v>
@@ -635,7 +628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B6" s="10"/>
       <c r="C6" s="6">
         <v>0</v>
@@ -662,7 +655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B7" s="10"/>
       <c r="C7" s="5">
         <v>0</v>
@@ -689,7 +682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B8" s="10"/>
       <c r="C8" s="5">
         <v>0</v>
@@ -715,8 +708,12 @@
       <c r="J8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="AD8" s="1">
+        <f>SUM(C5:J20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B9" s="10"/>
       <c r="C9" s="5">
         <v>0</v>
@@ -743,7 +740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B10" s="10"/>
       <c r="C10" s="5">
         <v>0</v>
@@ -770,7 +767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B11" s="10"/>
       <c r="C11" s="5">
         <v>0</v>
@@ -797,7 +794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B12" s="10"/>
       <c r="C12" s="5">
         <v>0</v>
@@ -824,7 +821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B13" s="10"/>
       <c r="C13" s="5">
         <v>0</v>
@@ -851,7 +848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B14" s="10"/>
       <c r="C14" s="5">
         <v>0</v>
@@ -878,7 +875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B15" s="10"/>
       <c r="C15" s="5">
         <v>0</v>
@@ -905,7 +902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B16" s="10"/>
       <c r="C16" s="5">
         <v>0</v>
@@ -4610,22 +4607,22 @@
     <mergeCell ref="B2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:J152">
-    <cfRule type="containsBlanks" dxfId="8" priority="6">
+    <cfRule type="containsBlanks" dxfId="7" priority="6">
       <formula>LEN(TRIM(B5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:J152">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:E152 G5:I152">
-    <cfRule type="cellIs" dxfId="6" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="23" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F152 J5:J152">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThan">
       <formula>64</formula>
     </cfRule>
   </conditionalFormatting>

--- a/School_Mang/EXCEL/Final/Term_A/Term_A_3_Test.xlsx
+++ b/School_Mang/EXCEL/Final/Term_A/Term_A_3_Test.xlsx
@@ -14,15 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>عربي</t>
   </si>
   <si>
     <t>دين</t>
-  </si>
-  <si>
-    <t>رياضيات</t>
   </si>
   <si>
     <t>دراسات</t>
@@ -44,6 +41,12 @@
   </si>
   <si>
     <t>الجلوس</t>
+  </si>
+  <si>
+    <t>جبر</t>
+  </si>
+  <si>
+    <t>هندسة</t>
   </si>
 </sst>
 </file>
@@ -167,36 +170,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF8B8B"/>
-          <bgColor rgb="FFFADF53"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC5C5"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -538,15 +512,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:AD152"/>
+  <dimension ref="A1:AD152"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="0" style="1" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" style="7" customWidth="1"/>
-    <col min="3" max="10" width="13.7109375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="11" width="13.7109375" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="D1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Z1" s="7"/>
+      <c r="AB1" s="7"/>
+      <c r="AD1" s="7"/>
+    </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -557,6 +547,7 @@
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
       <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
     </row>
     <row r="3" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="8"/>
@@ -568,13 +559,14 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>0</v>
@@ -583,22 +575,25 @@
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>7</v>
+      <c r="K4" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.3">
@@ -627,6 +622,13 @@
       <c r="J5" s="6">
         <v>0</v>
       </c>
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="1">
+        <f>E5+F5</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B6" s="10"/>
@@ -654,6 +656,13 @@
       <c r="J6" s="6">
         <v>0</v>
       </c>
+      <c r="K6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" ref="AC6:AC69" si="0">E6+F6</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B7" s="10"/>
@@ -681,6 +690,13 @@
       <c r="J7" s="5">
         <v>0</v>
       </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B8" s="10"/>
@@ -708,8 +724,15 @@
       <c r="J8" s="5">
         <v>0</v>
       </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="AD8" s="1">
-        <f>SUM(C5:J20)</f>
+        <f>SUM(C5:K20)</f>
         <v>0</v>
       </c>
     </row>
@@ -739,6 +762,13 @@
       <c r="J9" s="5">
         <v>0</v>
       </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B10" s="10"/>
@@ -766,6 +796,13 @@
       <c r="J10" s="5">
         <v>0</v>
       </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B11" s="10"/>
@@ -793,6 +830,13 @@
       <c r="J11" s="5">
         <v>0</v>
       </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B12" s="10"/>
@@ -820,6 +864,13 @@
       <c r="J12" s="5">
         <v>0</v>
       </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B13" s="10"/>
@@ -847,6 +898,13 @@
       <c r="J13" s="5">
         <v>0</v>
       </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B14" s="10"/>
@@ -874,6 +932,13 @@
       <c r="J14" s="5">
         <v>0</v>
       </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B15" s="10"/>
@@ -901,6 +966,13 @@
       <c r="J15" s="5">
         <v>0</v>
       </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B16" s="10"/>
@@ -928,8 +1000,15 @@
       <c r="J16" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B17" s="10"/>
       <c r="C17" s="5">
         <v>0</v>
@@ -955,8 +1034,15 @@
       <c r="J17" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B18" s="10"/>
       <c r="C18" s="5">
         <v>0</v>
@@ -982,8 +1068,15 @@
       <c r="J18" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B19" s="10"/>
       <c r="C19" s="5">
         <v>0</v>
@@ -1009,8 +1102,15 @@
       <c r="J19" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B20" s="10"/>
       <c r="C20" s="5">
         <v>0</v>
@@ -1036,8 +1136,15 @@
       <c r="J20" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K20" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B21" s="10"/>
       <c r="C21" s="5">
         <v>0</v>
@@ -1063,8 +1170,15 @@
       <c r="J21" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B22" s="10"/>
       <c r="C22" s="5">
         <v>0</v>
@@ -1090,8 +1204,15 @@
       <c r="J22" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B23" s="10"/>
       <c r="C23" s="5">
         <v>0</v>
@@ -1117,8 +1238,15 @@
       <c r="J23" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K23" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B24" s="10"/>
       <c r="C24" s="5">
         <v>0</v>
@@ -1144,8 +1272,15 @@
       <c r="J24" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B25" s="10"/>
       <c r="C25" s="5">
         <v>0</v>
@@ -1171,8 +1306,15 @@
       <c r="J25" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K25" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B26" s="10"/>
       <c r="C26" s="5">
         <v>0</v>
@@ -1198,8 +1340,15 @@
       <c r="J26" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K26" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B27" s="10"/>
       <c r="C27" s="5">
         <v>0</v>
@@ -1225,8 +1374,15 @@
       <c r="J27" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B28" s="10"/>
       <c r="C28" s="5">
         <v>0</v>
@@ -1252,8 +1408,15 @@
       <c r="J28" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K28" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B29" s="10"/>
       <c r="C29" s="5">
         <v>0</v>
@@ -1279,8 +1442,15 @@
       <c r="J29" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K29" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B30" s="10"/>
       <c r="C30" s="5">
         <v>0</v>
@@ -1306,8 +1476,15 @@
       <c r="J30" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K30" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B31" s="10"/>
       <c r="C31" s="5">
         <v>0</v>
@@ -1333,8 +1510,15 @@
       <c r="J31" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K31" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B32" s="10"/>
       <c r="C32" s="5">
         <v>0</v>
@@ -1360,8 +1544,15 @@
       <c r="J32" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K32" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B33" s="10"/>
       <c r="C33" s="5">
         <v>0</v>
@@ -1387,8 +1578,15 @@
       <c r="J33" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B34" s="10"/>
       <c r="C34" s="5">
         <v>0</v>
@@ -1414,8 +1612,15 @@
       <c r="J34" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K34" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B35" s="10"/>
       <c r="C35" s="5">
         <v>0</v>
@@ -1441,8 +1646,15 @@
       <c r="J35" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K35" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B36" s="10"/>
       <c r="C36" s="5">
         <v>0</v>
@@ -1468,8 +1680,15 @@
       <c r="J36" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K36" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B37" s="10"/>
       <c r="C37" s="5">
         <v>0</v>
@@ -1495,8 +1714,15 @@
       <c r="J37" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B38" s="10"/>
       <c r="C38" s="5">
         <v>0</v>
@@ -1522,8 +1748,15 @@
       <c r="J38" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K38" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B39" s="10"/>
       <c r="C39" s="5">
         <v>0</v>
@@ -1549,8 +1782,15 @@
       <c r="J39" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B40" s="10"/>
       <c r="C40" s="5">
         <v>0</v>
@@ -1576,8 +1816,15 @@
       <c r="J40" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B41" s="10"/>
       <c r="C41" s="5">
         <v>0</v>
@@ -1603,8 +1850,15 @@
       <c r="J41" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K41" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B42" s="10"/>
       <c r="C42" s="5">
         <v>0</v>
@@ -1630,8 +1884,15 @@
       <c r="J42" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B43" s="10"/>
       <c r="C43" s="5">
         <v>0</v>
@@ -1657,8 +1918,15 @@
       <c r="J43" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K43" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B44" s="10"/>
       <c r="C44" s="5">
         <v>0</v>
@@ -1684,8 +1952,15 @@
       <c r="J44" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K44" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B45" s="10"/>
       <c r="C45" s="5">
         <v>0</v>
@@ -1711,8 +1986,15 @@
       <c r="J45" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K45" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B46" s="10"/>
       <c r="C46" s="5">
         <v>0</v>
@@ -1738,8 +2020,15 @@
       <c r="J46" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B47" s="10"/>
       <c r="C47" s="5">
         <v>0</v>
@@ -1765,8 +2054,15 @@
       <c r="J47" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B48" s="10"/>
       <c r="C48" s="5">
         <v>0</v>
@@ -1792,8 +2088,15 @@
       <c r="J48" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K48" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B49" s="10"/>
       <c r="C49" s="5">
         <v>0</v>
@@ -1819,8 +2122,15 @@
       <c r="J49" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K49" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B50" s="10"/>
       <c r="C50" s="5">
         <v>0</v>
@@ -1846,8 +2156,15 @@
       <c r="J50" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B51" s="10"/>
       <c r="C51" s="5">
         <v>0</v>
@@ -1873,8 +2190,15 @@
       <c r="J51" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K51" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B52" s="10"/>
       <c r="C52" s="5">
         <v>0</v>
@@ -1900,8 +2224,15 @@
       <c r="J52" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K52" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B53" s="10"/>
       <c r="C53" s="5">
         <v>0</v>
@@ -1927,8 +2258,15 @@
       <c r="J53" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K53" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B54" s="10"/>
       <c r="C54" s="5">
         <v>0</v>
@@ -1954,8 +2292,15 @@
       <c r="J54" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K54" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B55" s="10"/>
       <c r="C55" s="5">
         <v>0</v>
@@ -1981,8 +2326,15 @@
       <c r="J55" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K55" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B56" s="10"/>
       <c r="C56" s="5">
         <v>0</v>
@@ -2008,8 +2360,15 @@
       <c r="J56" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B57" s="10"/>
       <c r="C57" s="5">
         <v>0</v>
@@ -2035,8 +2394,15 @@
       <c r="J57" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K57" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B58" s="10"/>
       <c r="C58" s="5">
         <v>0</v>
@@ -2062,8 +2428,15 @@
       <c r="J58" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K58" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B59" s="10"/>
       <c r="C59" s="5">
         <v>0</v>
@@ -2089,8 +2462,15 @@
       <c r="J59" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K59" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B60" s="10"/>
       <c r="C60" s="5">
         <v>0</v>
@@ -2116,8 +2496,15 @@
       <c r="J60" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B61" s="10"/>
       <c r="C61" s="5">
         <v>0</v>
@@ -2143,8 +2530,15 @@
       <c r="J61" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K61" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B62" s="10"/>
       <c r="C62" s="5">
         <v>0</v>
@@ -2170,8 +2564,15 @@
       <c r="J62" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K62" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B63" s="10"/>
       <c r="C63" s="5">
         <v>0</v>
@@ -2197,8 +2598,15 @@
       <c r="J63" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B64" s="10"/>
       <c r="C64" s="5">
         <v>0</v>
@@ -2224,8 +2632,15 @@
       <c r="J64" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B65" s="10"/>
       <c r="C65" s="5">
         <v>0</v>
@@ -2251,8 +2666,15 @@
       <c r="J65" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K65" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B66" s="10"/>
       <c r="C66" s="5">
         <v>0</v>
@@ -2278,8 +2700,15 @@
       <c r="J66" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K66" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B67" s="10"/>
       <c r="C67" s="5">
         <v>0</v>
@@ -2305,8 +2734,15 @@
       <c r="J67" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K67" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B68" s="10"/>
       <c r="C68" s="5">
         <v>0</v>
@@ -2332,8 +2768,15 @@
       <c r="J68" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K68" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B69" s="10"/>
       <c r="C69" s="5">
         <v>0</v>
@@ -2359,8 +2802,15 @@
       <c r="J69" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K69" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B70" s="10"/>
       <c r="C70" s="5">
         <v>0</v>
@@ -2386,8 +2836,15 @@
       <c r="J70" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K70" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="1">
+        <f t="shared" ref="AC70:AC133" si="1">E70+F70</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B71" s="10"/>
       <c r="C71" s="5">
         <v>0</v>
@@ -2413,8 +2870,15 @@
       <c r="J71" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K71" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B72" s="10"/>
       <c r="C72" s="5">
         <v>0</v>
@@ -2440,8 +2904,15 @@
       <c r="J72" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K72" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC72" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B73" s="10"/>
       <c r="C73" s="5">
         <v>0</v>
@@ -2467,8 +2938,15 @@
       <c r="J73" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K73" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B74" s="10"/>
       <c r="C74" s="5">
         <v>0</v>
@@ -2494,8 +2972,15 @@
       <c r="J74" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K74" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B75" s="10"/>
       <c r="C75" s="5">
         <v>0</v>
@@ -2521,8 +3006,15 @@
       <c r="J75" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K75" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B76" s="10"/>
       <c r="C76" s="5">
         <v>0</v>
@@ -2548,8 +3040,15 @@
       <c r="J76" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K76" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B77" s="10"/>
       <c r="C77" s="5">
         <v>0</v>
@@ -2575,8 +3074,15 @@
       <c r="J77" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K77" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B78" s="10"/>
       <c r="C78" s="5">
         <v>0</v>
@@ -2602,8 +3108,15 @@
       <c r="J78" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K78" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B79" s="10"/>
       <c r="C79" s="5">
         <v>0</v>
@@ -2629,8 +3142,15 @@
       <c r="J79" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K79" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B80" s="10"/>
       <c r="C80" s="5">
         <v>0</v>
@@ -2656,8 +3176,15 @@
       <c r="J80" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K80" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B81" s="10"/>
       <c r="C81" s="5">
         <v>0</v>
@@ -2683,8 +3210,15 @@
       <c r="J81" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K81" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B82" s="10"/>
       <c r="C82" s="5">
         <v>0</v>
@@ -2710,8 +3244,15 @@
       <c r="J82" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K82" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B83" s="10"/>
       <c r="C83" s="5">
         <v>0</v>
@@ -2737,8 +3278,15 @@
       <c r="J83" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K83" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B84" s="10"/>
       <c r="C84" s="5">
         <v>0</v>
@@ -2764,8 +3312,15 @@
       <c r="J84" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K84" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B85" s="10"/>
       <c r="C85" s="5">
         <v>0</v>
@@ -2791,8 +3346,15 @@
       <c r="J85" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K85" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B86" s="10"/>
       <c r="C86" s="5">
         <v>0</v>
@@ -2818,8 +3380,15 @@
       <c r="J86" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K86" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B87" s="10"/>
       <c r="C87" s="5">
         <v>0</v>
@@ -2845,8 +3414,15 @@
       <c r="J87" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K87" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B88" s="10"/>
       <c r="C88" s="5">
         <v>0</v>
@@ -2872,8 +3448,15 @@
       <c r="J88" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K88" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B89" s="10"/>
       <c r="C89" s="5">
         <v>0</v>
@@ -2899,8 +3482,15 @@
       <c r="J89" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K89" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B90" s="10"/>
       <c r="C90" s="5">
         <v>0</v>
@@ -2926,8 +3516,15 @@
       <c r="J90" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K90" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B91" s="10"/>
       <c r="C91" s="5">
         <v>0</v>
@@ -2953,8 +3550,15 @@
       <c r="J91" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K91" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B92" s="10"/>
       <c r="C92" s="5">
         <v>0</v>
@@ -2980,8 +3584,15 @@
       <c r="J92" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K92" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B93" s="10"/>
       <c r="C93" s="5">
         <v>0</v>
@@ -3007,8 +3618,15 @@
       <c r="J93" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K93" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B94" s="10"/>
       <c r="C94" s="5">
         <v>0</v>
@@ -3034,8 +3652,15 @@
       <c r="J94" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K94" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B95" s="10"/>
       <c r="C95" s="5">
         <v>0</v>
@@ -3061,8 +3686,15 @@
       <c r="J95" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K95" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC95" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B96" s="10"/>
       <c r="C96" s="5">
         <v>0</v>
@@ -3088,8 +3720,15 @@
       <c r="J96" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K96" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B97" s="10"/>
       <c r="C97" s="5">
         <v>0</v>
@@ -3115,8 +3754,15 @@
       <c r="J97" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K97" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B98" s="10"/>
       <c r="C98" s="5">
         <v>0</v>
@@ -3142,8 +3788,15 @@
       <c r="J98" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K98" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B99" s="10"/>
       <c r="C99" s="5">
         <v>0</v>
@@ -3169,8 +3822,15 @@
       <c r="J99" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K99" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B100" s="10"/>
       <c r="C100" s="5">
         <v>0</v>
@@ -3196,8 +3856,15 @@
       <c r="J100" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K100" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B101" s="10"/>
       <c r="C101" s="5">
         <v>0</v>
@@ -3223,8 +3890,15 @@
       <c r="J101" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K101" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B102" s="10"/>
       <c r="C102" s="5">
         <v>0</v>
@@ -3250,8 +3924,15 @@
       <c r="J102" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K102" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B103" s="10"/>
       <c r="C103" s="5">
         <v>0</v>
@@ -3277,8 +3958,15 @@
       <c r="J103" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K103" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC103" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B104" s="10"/>
       <c r="C104" s="5">
         <v>0</v>
@@ -3304,8 +3992,15 @@
       <c r="J104" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K104" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC104" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B105" s="10"/>
       <c r="C105" s="5">
         <v>0</v>
@@ -3331,8 +4026,15 @@
       <c r="J105" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K105" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC105" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B106" s="10"/>
       <c r="C106" s="5">
         <v>0</v>
@@ -3358,8 +4060,15 @@
       <c r="J106" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K106" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC106" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B107" s="10"/>
       <c r="C107" s="5">
         <v>0</v>
@@ -3385,8 +4094,15 @@
       <c r="J107" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K107" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC107" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B108" s="10"/>
       <c r="C108" s="5">
         <v>0</v>
@@ -3412,8 +4128,15 @@
       <c r="J108" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K108" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC108" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B109" s="10"/>
       <c r="C109" s="5">
         <v>0</v>
@@ -3439,8 +4162,15 @@
       <c r="J109" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K109" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC109" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B110" s="10"/>
       <c r="C110" s="5">
         <v>0</v>
@@ -3466,8 +4196,15 @@
       <c r="J110" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K110" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC110" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B111" s="10"/>
       <c r="C111" s="5">
         <v>0</v>
@@ -3493,8 +4230,15 @@
       <c r="J111" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K111" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B112" s="10"/>
       <c r="C112" s="5">
         <v>0</v>
@@ -3520,8 +4264,15 @@
       <c r="J112" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K112" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC112" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B113" s="10"/>
       <c r="C113" s="5">
         <v>0</v>
@@ -3547,8 +4298,15 @@
       <c r="J113" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K113" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC113" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B114" s="10"/>
       <c r="C114" s="5">
         <v>0</v>
@@ -3574,8 +4332,15 @@
       <c r="J114" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K114" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC114" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B115" s="10"/>
       <c r="C115" s="5">
         <v>0</v>
@@ -3601,8 +4366,15 @@
       <c r="J115" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K115" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC115" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B116" s="10"/>
       <c r="C116" s="5">
         <v>0</v>
@@ -3628,8 +4400,15 @@
       <c r="J116" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K116" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B117" s="10"/>
       <c r="C117" s="5">
         <v>0</v>
@@ -3655,8 +4434,15 @@
       <c r="J117" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K117" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC117" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B118" s="10"/>
       <c r="C118" s="5">
         <v>0</v>
@@ -3682,8 +4468,15 @@
       <c r="J118" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K118" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC118" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B119" s="10"/>
       <c r="C119" s="5">
         <v>0</v>
@@ -3709,8 +4502,15 @@
       <c r="J119" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K119" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC119" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B120" s="10"/>
       <c r="C120" s="5">
         <v>0</v>
@@ -3736,8 +4536,15 @@
       <c r="J120" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K120" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC120" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B121" s="10"/>
       <c r="C121" s="5">
         <v>0</v>
@@ -3763,8 +4570,15 @@
       <c r="J121" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K121" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC121" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B122" s="10"/>
       <c r="C122" s="5">
         <v>0</v>
@@ -3790,8 +4604,15 @@
       <c r="J122" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K122" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC122" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B123" s="10"/>
       <c r="C123" s="5">
         <v>0</v>
@@ -3817,8 +4638,15 @@
       <c r="J123" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K123" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC123" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B124" s="10"/>
       <c r="C124" s="5">
         <v>0</v>
@@ -3844,8 +4672,15 @@
       <c r="J124" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K124" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC124" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B125" s="10"/>
       <c r="C125" s="5">
         <v>0</v>
@@ -3871,8 +4706,15 @@
       <c r="J125" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K125" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC125" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B126" s="10"/>
       <c r="C126" s="5">
         <v>0</v>
@@ -3898,8 +4740,15 @@
       <c r="J126" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K126" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC126" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B127" s="10"/>
       <c r="C127" s="5">
         <v>0</v>
@@ -3925,8 +4774,15 @@
       <c r="J127" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K127" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC127" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B128" s="10"/>
       <c r="C128" s="5">
         <v>0</v>
@@ -3952,8 +4808,15 @@
       <c r="J128" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K128" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC128" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B129" s="10"/>
       <c r="C129" s="5">
         <v>0</v>
@@ -3979,8 +4842,15 @@
       <c r="J129" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K129" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC129" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B130" s="10"/>
       <c r="C130" s="5">
         <v>0</v>
@@ -4006,8 +4876,15 @@
       <c r="J130" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K130" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC130" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B131" s="10"/>
       <c r="C131" s="5">
         <v>0</v>
@@ -4033,8 +4910,15 @@
       <c r="J131" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K131" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC131" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B132" s="10"/>
       <c r="C132" s="5">
         <v>0</v>
@@ -4060,8 +4944,15 @@
       <c r="J132" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K132" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC132" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B133" s="10"/>
       <c r="C133" s="5">
         <v>0</v>
@@ -4087,8 +4978,15 @@
       <c r="J133" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K133" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC133" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B134" s="10"/>
       <c r="C134" s="5">
         <v>0</v>
@@ -4114,8 +5012,15 @@
       <c r="J134" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K134" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC134" s="1">
+        <f t="shared" ref="AC134:AC152" si="2">E134+F134</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B135" s="10"/>
       <c r="C135" s="5">
         <v>0</v>
@@ -4141,8 +5046,15 @@
       <c r="J135" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K135" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC135" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B136" s="10"/>
       <c r="C136" s="5">
         <v>0</v>
@@ -4168,8 +5080,15 @@
       <c r="J136" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K136" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC136" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B137" s="10"/>
       <c r="C137" s="5">
         <v>0</v>
@@ -4195,8 +5114,15 @@
       <c r="J137" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K137" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC137" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B138" s="10"/>
       <c r="C138" s="5">
         <v>0</v>
@@ -4222,8 +5148,15 @@
       <c r="J138" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K138" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC138" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B139" s="10"/>
       <c r="C139" s="5">
         <v>0</v>
@@ -4249,8 +5182,15 @@
       <c r="J139" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K139" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC139" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B140" s="10"/>
       <c r="C140" s="5">
         <v>0</v>
@@ -4276,8 +5216,15 @@
       <c r="J140" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K140" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC140" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B141" s="10"/>
       <c r="C141" s="5">
         <v>0</v>
@@ -4303,8 +5250,15 @@
       <c r="J141" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K141" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC141" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B142" s="10"/>
       <c r="C142" s="5">
         <v>0</v>
@@ -4330,8 +5284,15 @@
       <c r="J142" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K142" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC142" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B143" s="10"/>
       <c r="C143" s="5">
         <v>0</v>
@@ -4357,8 +5318,15 @@
       <c r="J143" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K143" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC143" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B144" s="10"/>
       <c r="C144" s="5">
         <v>0</v>
@@ -4384,8 +5352,15 @@
       <c r="J144" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K144" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC144" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B145" s="10"/>
       <c r="C145" s="5">
         <v>0</v>
@@ -4411,8 +5386,15 @@
       <c r="J145" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K145" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC145" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B146" s="10"/>
       <c r="C146" s="5">
         <v>0</v>
@@ -4438,8 +5420,15 @@
       <c r="J146" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K146" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC146" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B147" s="10"/>
       <c r="C147" s="5">
         <v>0</v>
@@ -4465,8 +5454,15 @@
       <c r="J147" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K147" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC147" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B148" s="10"/>
       <c r="C148" s="5">
         <v>0</v>
@@ -4492,8 +5488,15 @@
       <c r="J148" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K148" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC148" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B149" s="10"/>
       <c r="C149" s="5">
         <v>0</v>
@@ -4519,8 +5522,15 @@
       <c r="J149" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K149" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC149" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B150" s="10"/>
       <c r="C150" s="5">
         <v>0</v>
@@ -4546,8 +5556,15 @@
       <c r="J150" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K150" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC150" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B151" s="10"/>
       <c r="C151" s="5">
         <v>0</v>
@@ -4573,8 +5590,15 @@
       <c r="J151" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K151" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B152" s="10"/>
       <c r="C152" s="5">
         <v>0</v>
@@ -4598,31 +5622,38 @@
         <v>0</v>
       </c>
       <c r="J152" s="5">
+        <v>0</v>
+      </c>
+      <c r="K152" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC152" s="1">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="1">
-    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:J152">
-    <cfRule type="containsBlanks" dxfId="7" priority="6">
+  <conditionalFormatting sqref="B5:K152">
+    <cfRule type="containsBlanks" dxfId="3" priority="6">
       <formula>LEN(TRIM(B5))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C5:J152">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+  <conditionalFormatting sqref="C5:K152">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C5:E152 G5:I152">
-    <cfRule type="cellIs" dxfId="5" priority="23" operator="greaterThan">
+  <conditionalFormatting sqref="C5:F152 H5:J152">
+    <cfRule type="cellIs" dxfId="1" priority="23" operator="greaterThan">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F152 J5:J152">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThan">
+  <conditionalFormatting sqref="G5:G152 K5:K152">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
       <formula>64</formula>
     </cfRule>
   </conditionalFormatting>

--- a/School_Mang/EXCEL/Final/Term_A/Term_A_3_Test.xlsx
+++ b/School_Mang/EXCEL/Final/Term_A/Term_A_3_Test.xlsx
@@ -170,7 +170,36 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF8B8B"/>
+          <bgColor rgb="FFFADF53"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC5C5"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5638,22 +5667,22 @@
     <mergeCell ref="B2:K2"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:K152">
-    <cfRule type="containsBlanks" dxfId="3" priority="6">
+    <cfRule type="containsBlanks" dxfId="7" priority="6">
       <formula>LEN(TRIM(B5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:K152">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:F152 H5:J152">
-    <cfRule type="cellIs" dxfId="1" priority="23" operator="greaterThan">
-      <formula>80</formula>
+    <cfRule type="cellIs" dxfId="4" priority="23" operator="greaterThan">
+      <formula>30</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G152 K5:K152">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>64</formula>
     </cfRule>
   </conditionalFormatting>
